--- a/KS_year1_awardees.xlsx
+++ b/KS_year1_awardees.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve">Read this before using any figure</t>
   </si>
   <si>
-    <t xml:space="preserve">Kansas Year 1: 46 award actions, $80,020,499, across THREE pools KDHE published in TWO documents.</t>
+    <t xml:space="preserve">Kansas Year 1: 46 award actions, $96,027,147, across THREE pools KDHE published in TWO documents.</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">pipeline's own knowledge; the CCN match resolves them.</t>
   </si>
   <si>
-    <t xml:space="preserve">RCJ HOLDS 45 OF THESE 46 AWARDS. Every amount it holds matches the state</t>
+    <t xml:space="preserve">RCJ HOLDS 45 OF THESE 60 AWARDS. Every amount it holds matches the state</t>
   </si>
   <si>
     <t xml:space="preserve">document exactly; the one it dropped is Greeley County's REH CAP award,</t>
@@ -181,6 +181,15 @@
     <t xml:space="preserve">source_archive_path</t>
   </si>
   <si>
+    <t xml:space="preserve">basis_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verified_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verified_basis</t>
+  </si>
+  <si>
     <t xml:space="preserve">KS</t>
   </si>
   <si>
@@ -455,6 +464,204 @@
   </si>
   <si>
     <t xml:space="preserve">Newman Memorial County Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommonSpirit Kansas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS Hospital enrolment ORGANIZATION NAME 'COMMONSPIRIT KANSAS INC', Garden City (Finney County, this award's county); it also enrols a CAH in Ulysses. Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerging Technology Award Winners and Project Descriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMERGING_TECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS Hospital enrolment ORGANIZATION NAME 'COMMONSPIRIT KANSAS INC', Garden City (Finney County, this award's county); it also enrols a CAH in Ulysses. Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/KS/2026-09-22_kdhe_emerging_technology_award_winners.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORG_WEBSITE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">session 52 (hand-read against CMS enrolment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital enrolment ORGANIZATION NAME 'COMMONSPIRIT KANSAS INC', Garden City (Finney County, this award's county); it also enrols a CAH in Ulysses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UKHS Great Bend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS Hospital enrolment ORGANIZATION NAME 'UKHS GREAT BEND LLC', Great Bend (Barton County). Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS Hospital enrolment ORGANIZATION NAME 'UKHS GREAT BEND LLC', Great Bend (Barton County). Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital enrolment ORGANIZATION NAME 'UKHS GREAT BEND LLC', Great Bend (Barton County)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rooks County Health Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS CRITICAL ACCESS HOSPITAL enrolment, ORGANIZATION NAME, Plainville (Rooks County). Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS CRITICAL ACCESS HOSPITAL enrolment, ORGANIZATION NAME, Plainville (Rooks County). Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS CRITICAL ACCESS HOSPITAL enrolment, ORGANIZATION NAME, Plainville (Rooks County)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital District #1 Rice County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [GENERAL_KNOWLEDGE] -- BRIDGE: CMS enrols 'HOSPITAL DISTRICT NO 1 OF RICE CO' as a CRITICAL ACCESS HOSPITAL in Lyons (Rice County); '#1' for 'No 1' and 'Rice County' for 'of Rice Co' is a reading, not an exact string. Flow: DIRECT. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [GENERAL_KNOWLEDGE] -- BRIDGE: CMS enrols 'HOSPITAL DISTRICT NO 1 OF RICE CO' as a CRITICAL ACCESS HOSPITAL in Lyons (Rice County); '#1' for 'No 1' and 'Rice County' for 'of Rice Co' is a reading, not an exact string. Flow: DIRECT. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERAL_KNOWLEDGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIDGE: CMS enrols 'HOSPITAL DISTRICT NO 1 OF RICE CO' as a CRITICAL ACCESS HOSPITAL in Lyons (Rice County); '#1' for 'No 1' and 'Rice County' for 'of Rice Co' is a reading, not an exact string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoodLife Innovations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE REFUSED (session 52): no archived CMS enrolment carries this recipient and KDHE states no form; §8's standing fallback. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE REFUSED (session 52): no archived CMS enrolment carries this recipient and KDHE states no form; §8's standing fallback. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via Christi Village Hays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): OTHER [ORG_WEBSITE] -- A SKILLED NURSING FACILITY: CMS SNF enrolment 'VIA CHRISTI VILLAGE HAYS KS LLC' dba 'VIA CHRISTI VILLAGE HAYS', Hays (Ellis County). KDHE's description agrees: '16 participating rural skilled nursing and long-term care facilities'. Flow: NON_HOSPITAL. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): OTHER [ORG_WEBSITE] -- A SKILLED NURSING FACILITY: CMS SNF enrolment 'VIA CHRISTI VILLAGE HAYS KS LLC' dba 'VIA CHRISTI VILLAGE HAYS', Hays (Ellis County). KDHE's description agrees: '16 participating rural skilled nursing and long-term care facilities'. Flow: NON_HOSPITAL. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A SKILLED NURSING FACILITY: CMS SNF enrolment 'VIA CHRISTI VILLAGE HAYS KS LLC' dba 'VIA CHRISTI VILLAGE HAYS', Hays (Ellis County). KDHE's description agrees: '16 participating rural skilled nursing and long-term care facilities'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genesis Family Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FQHC_OR_RHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): FQHC_OR_RHC [STATE_SOURCE] -- KDHE's own description: 'GFH, a federally qualified health center'; CMS FQHC enrolment DBA 'GENESIS FAMILY HEALTH' agrees. Flow: NON_HOSPITAL. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): FQHC_OR_RHC [STATE_SOURCE] -- KDHE's own description: 'GFH, a federally qualified health center'; CMS FQHC enrolment DBA 'GENESIS FAMILY HEALTH' agrees. Flow: NON_HOSPITAL. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATE_SOURCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE's own description: 'GFH, a federally qualified health center'; CMS FQHC enrolment DBA 'GENESIS FAMILY HEALTH' agrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumner Mental Health Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): OTHER [STATE_SOURCE] -- A COMMUNITY MENTAL HEALTH CENTRE: the award string itself names a mental health center (session 50 typed Mississippi's CMHCs OTHER on the same footing). Flow: NON_HOSPITAL. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): OTHER [STATE_SOURCE] -- A COMMUNITY MENTAL HEALTH CENTRE: the award string itself names a mental health center (session 50 typed Mississippi's CMHCs OTHER on the same footing). Flow: NON_HOSPITAL. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A COMMUNITY MENTAL HEALTH CENTRE: the award string itself names a mental health center (session 50 typed Mississippi's CMHCs OTHER on the same footing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prairie View Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMC Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS Hospital enrolment DBA 'NMC HEALTH', Newton (Harvey County). Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS Hospital enrolment DBA 'NMC HEALTH', Newton (Harvey County). Flow: DIRECT. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital enrolment DBA 'NMC HEALTH', Newton (Harvey County)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attica Hospital District #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE REFUSED (session 52): no archived CMS enrolment carries this recipient and KDHE states no form; §8's standing fallback. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE REFUSED (session 52): no archived CMS enrolment carries this recipient and KDHE states no form; §8's standing fallback. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grisell Memorial Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [GENERAL_KNOWLEDGE] -- BRIDGE: CMS enrols 'GRISELL MEMORIAL HOSPITAL DISTRICT 1' as a CRITICAL ACCESS HOSPITAL in Ransom (Ness County, this award's county); the award string drops 'District 1'. Flow: DIRECT. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [GENERAL_KNOWLEDGE] -- BRIDGE: CMS enrols 'GRISELL MEMORIAL HOSPITAL DISTRICT 1' as a CRITICAL ACCESS HOSPITAL in Ransom (Ness County, this award's county); the award string drops 'District 1'. Flow: DIRECT. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIDGE: CMS enrols 'GRISELL MEMORIAL HOSPITAL DISTRICT 1' as a CRITICAL ACCESS HOSPITAL in Ransom (Ness County, this award's county); the award string drops 'District 1'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valley Hope Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meade Hospital District</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDHE EMERGING_TECH award. RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS CRITICAL ACCESS HOSPITAL enrolment, ORGANIZATION NAME, Meade (Meade County). Flow: DIRECT. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT TYPE (session 52): HOSPITAL_OR_SYSTEM [ORG_WEBSITE] -- CMS CRITICAL ACCESS HOSPITAL enrolment, ORGANIZATION NAME, Meade (Meade County). Flow: DIRECT. Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS CRITICAL ACCESS HOSPITAL enrolment, ORGANIZATION NAME, Meade (Meade County)</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
@@ -1045,3547 +1252,4884 @@
       <c r="AB1" t="s">
         <v>54</v>
       </c>
+      <c r="AC1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
         <v>3000000</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2"/>
       <c r="T2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA2"/>
       <c r="AB2" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D3" t="n">
         <v>3000000</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3"/>
       <c r="T3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA3"/>
       <c r="AB3" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D4" t="n">
         <v>2933500</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4"/>
       <c r="T4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA4"/>
       <c r="AB4" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D5" t="n">
         <v>2869082</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5"/>
       <c r="T5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA5"/>
       <c r="AB5" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
         <v>2502999</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6"/>
       <c r="T6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA6"/>
       <c r="AB6" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D7" t="n">
         <v>2478316</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7"/>
       <c r="T7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA7"/>
       <c r="AB7" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D8" t="n">
         <v>2378188</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8"/>
       <c r="T8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D9" t="n">
         <v>2145677</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
       <c r="R9"/>
       <c r="S9"/>
       <c r="T9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D10" t="n">
         <v>1987287</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
       <c r="R10"/>
       <c r="S10"/>
       <c r="T10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB10" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
         <v>1555143</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
       <c r="R11"/>
       <c r="S11"/>
       <c r="T11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA11"/>
       <c r="AB11" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B12" t="n">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>1500000</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12"/>
       <c r="S12"/>
       <c r="T12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA12"/>
       <c r="AB12" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
         <v>837000</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13"/>
       <c r="S13"/>
       <c r="T13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA13"/>
       <c r="AB13" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
         <v>550000</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
       <c r="T14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA14"/>
       <c r="AB14" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" t="n">
         <v>458286</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15"/>
       <c r="S15"/>
       <c r="T15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B16" t="n">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D16" t="n">
         <v>375981</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16"/>
       <c r="T16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA16"/>
       <c r="AB16" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D17" t="n">
         <v>361478</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
       <c r="R17"/>
       <c r="S17"/>
       <c r="T17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA17"/>
       <c r="AB17" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B18" t="n">
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D18" t="n">
         <v>165000</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18"/>
       <c r="S18"/>
       <c r="T18" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB18" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19" t="n">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>6096062</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P19"/>
       <c r="Q19"/>
       <c r="R19"/>
       <c r="S19"/>
       <c r="T19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA19"/>
       <c r="AB19" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B20" t="n">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>5465969</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K20" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N20" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
       <c r="R20"/>
       <c r="S20"/>
       <c r="T20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB20" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>5000000</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
       <c r="R21"/>
       <c r="S21"/>
       <c r="T21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U21" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB21" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" t="n">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D22" t="n">
         <v>4290000</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J22" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N22" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P22"/>
       <c r="Q22"/>
       <c r="R22"/>
       <c r="S22"/>
       <c r="T22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA22" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB22" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D23" t="n">
         <v>3439901</v>
       </c>
       <c r="E23" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M23" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N23" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P23"/>
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23"/>
       <c r="T23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Z23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA23"/>
       <c r="AB23" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" t="n">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D24" t="n">
         <v>2832423</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M24" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N24" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O24" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P24"/>
       <c r="Q24"/>
       <c r="R24"/>
       <c r="S24"/>
       <c r="T24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB24" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC24"/>
+      <c r="AD24"/>
+      <c r="AE24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D25" t="n">
         <v>2546981</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N25" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P25"/>
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25"/>
       <c r="T25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U25" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA25" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB25" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC25"/>
+      <c r="AD25"/>
+      <c r="AE25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B26" t="n">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D26" t="n">
         <v>2536000</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G26" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M26" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N26" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
       <c r="R26"/>
       <c r="S26"/>
       <c r="T26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U26" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W26" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X26" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA26"/>
       <c r="AB26" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B27" t="n">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D27" t="n">
         <v>2500000</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N27" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P27"/>
       <c r="Q27"/>
       <c r="R27"/>
       <c r="S27"/>
       <c r="T27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U27" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W27" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA27"/>
       <c r="AB27" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC27"/>
+      <c r="AD27"/>
+      <c r="AE27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B28" t="n">
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D28" t="n">
         <v>2028980</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K28" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L28" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
       <c r="R28"/>
       <c r="S28"/>
       <c r="T28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB28" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B29" t="n">
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D29" t="n">
         <v>1720957</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J29" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K29" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N29" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
       <c r="R29"/>
       <c r="S29"/>
       <c r="T29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U29" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X29" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA29" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB29" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B30" t="n">
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D30" t="n">
         <v>1660879</v>
       </c>
       <c r="E30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U30" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB30" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B31" t="n">
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D31" t="n">
         <v>1541906</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I31" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L31" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M31" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N31" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O31" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31"/>
       <c r="S31"/>
       <c r="T31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V31" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z31" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA31" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB31" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B32" t="n">
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D32" t="n">
         <v>1460000</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I32" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K32" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L32" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M32" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O32" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32"/>
       <c r="T32" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U32" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W32" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y32" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z32" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA32" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB32" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B33" t="n">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D33" t="n">
         <v>1395814</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K33" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L33" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M33" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O33" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P33"/>
       <c r="Q33"/>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X33" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z33" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA33" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB33" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B34" t="n">
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D34" t="n">
         <v>1383289</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K34" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L34" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M34" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N34" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O34" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34"/>
       <c r="S34"/>
       <c r="T34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U34" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W34" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X34" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA34"/>
       <c r="AB34" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B35" t="n">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D35" t="n">
         <v>1354975</v>
       </c>
       <c r="E35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F35" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J35" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M35" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N35" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O35" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35"/>
       <c r="S35"/>
       <c r="T35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U35" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V35" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA35" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB35" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B36" t="n">
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D36" t="n">
         <v>932310</v>
       </c>
       <c r="E36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F36" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I36" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K36" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L36" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M36" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O36" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36"/>
       <c r="T36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V36" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W36" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X36" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y36" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z36" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA36" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB36" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D37" t="n">
         <v>681711</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G37" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I37" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K37" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L37" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M37" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N37" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O37" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P37"/>
       <c r="Q37"/>
       <c r="R37"/>
       <c r="S37"/>
       <c r="T37" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U37" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V37" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W37" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X37" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y37" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA37"/>
       <c r="AB37" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B38" t="n">
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D38" t="n">
         <v>677248</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K38" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L38" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M38" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N38" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38"/>
       <c r="S38"/>
       <c r="T38" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W38" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X38" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y38" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Z38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA38"/>
       <c r="AB38" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B39" t="n">
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D39" t="n">
         <v>196650</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I39" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J39" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L39" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M39" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N39" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O39" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P39"/>
       <c r="Q39"/>
       <c r="R39"/>
       <c r="S39"/>
       <c r="T39" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U39" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W39" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X39" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z39" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA39" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB39" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B40" t="n">
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D40" t="n">
         <v>173355</v>
       </c>
       <c r="E40" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I40" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J40" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K40" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L40" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M40" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N40" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O40" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P40"/>
       <c r="Q40"/>
       <c r="R40"/>
       <c r="S40"/>
       <c r="T40" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="U40" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W40" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X40" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y40" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z40" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA40" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB40" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AC40"/>
+      <c r="AD40"/>
+      <c r="AE40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D41" t="n">
         <v>150000</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I41" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J41" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K41" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L41" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M41" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N41" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O41" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P41"/>
       <c r="Q41"/>
       <c r="R41"/>
       <c r="S41"/>
       <c r="T41" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U41" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V41" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W41" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA41"/>
       <c r="AB41" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B42" t="n">
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D42" t="n">
         <v>150000</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J42" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M42" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N42" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O42" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P42"/>
       <c r="Q42"/>
       <c r="R42"/>
       <c r="S42"/>
       <c r="T42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U42" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W42" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X42" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y42" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA42"/>
       <c r="AB42" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC42"/>
+      <c r="AD42"/>
+      <c r="AE42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B43" t="n">
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D43" t="n">
         <v>150000</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I43" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P43"/>
       <c r="Q43"/>
       <c r="R43"/>
       <c r="S43"/>
       <c r="T43" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V43" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X43" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y43" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA43" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB43" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B44" t="n">
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D44" t="n">
         <v>150000</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G44" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J44" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K44" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M44" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N44" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O44" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P44"/>
       <c r="Q44"/>
       <c r="R44"/>
       <c r="S44"/>
       <c r="T44" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U44" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W44" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X44" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y44" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA44"/>
       <c r="AB44" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC44"/>
+      <c r="AD44"/>
+      <c r="AE44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B45" t="n">
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D45" t="n">
         <v>149960</v>
       </c>
       <c r="E45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F45" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I45" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J45" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K45" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M45" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N45" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O45" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P45"/>
       <c r="Q45"/>
       <c r="R45"/>
       <c r="S45"/>
       <c r="T45" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U45" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V45" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W45" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X45" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y45" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z45" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA45" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB45" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B46" t="n">
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D46" t="n">
         <v>146476</v>
       </c>
       <c r="E46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I46" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J46" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M46" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N46" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O46" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P46"/>
       <c r="Q46"/>
       <c r="R46"/>
       <c r="S46"/>
       <c r="T46" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U46" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V46" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W46" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X46" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z46" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AA46" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB46" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B47" t="n">
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D47" t="n">
         <v>110716</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G47" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I47" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K47" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M47" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N47" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O47" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P47"/>
       <c r="Q47"/>
       <c r="R47"/>
       <c r="S47"/>
       <c r="T47" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U47" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V47" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W47" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X47" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y47" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA47"/>
       <c r="AB47" t="s">
-        <v>138</v>
+        <v>141</v>
+      </c>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2980250</v>
+      </c>
+      <c r="E48" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48" t="s">
+        <v>151</v>
+      </c>
+      <c r="H48" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" t="s">
+        <v>61</v>
+      </c>
+      <c r="J48" t="s">
+        <v>63</v>
+      </c>
+      <c r="K48" t="s">
+        <v>152</v>
+      </c>
+      <c r="L48" t="s">
+        <v>65</v>
+      </c>
+      <c r="M48" t="s">
+        <v>66</v>
+      </c>
+      <c r="N48" t="s">
+        <v>67</v>
+      </c>
+      <c r="O48" t="s">
+        <v>68</v>
+      </c>
+      <c r="P48" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="T48" t="s">
+        <v>154</v>
+      </c>
+      <c r="U48" t="s">
+        <v>70</v>
+      </c>
+      <c r="V48" t="s">
+        <v>61</v>
+      </c>
+      <c r="W48" t="s">
+        <v>71</v>
+      </c>
+      <c r="X48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA48"/>
+      <c r="AB48" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2960927</v>
+      </c>
+      <c r="E49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K49" t="s">
+        <v>152</v>
+      </c>
+      <c r="L49" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" t="s">
+        <v>66</v>
+      </c>
+      <c r="N49" t="s">
+        <v>67</v>
+      </c>
+      <c r="O49" t="s">
+        <v>68</v>
+      </c>
+      <c r="P49" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q49"/>
+      <c r="R49"/>
+      <c r="S49"/>
+      <c r="T49" t="s">
+        <v>154</v>
+      </c>
+      <c r="U49" t="s">
+        <v>70</v>
+      </c>
+      <c r="V49" t="s">
+        <v>61</v>
+      </c>
+      <c r="W49" t="s">
+        <v>71</v>
+      </c>
+      <c r="X49" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA49"/>
+      <c r="AB49" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>165</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1704066</v>
+      </c>
+      <c r="E50" t="s">
+        <v>60</v>
+      </c>
+      <c r="F50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" t="s">
+        <v>166</v>
+      </c>
+      <c r="H50" t="s">
+        <v>61</v>
+      </c>
+      <c r="I50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J50" t="s">
+        <v>63</v>
+      </c>
+      <c r="K50" t="s">
+        <v>152</v>
+      </c>
+      <c r="L50" t="s">
+        <v>65</v>
+      </c>
+      <c r="M50" t="s">
+        <v>66</v>
+      </c>
+      <c r="N50" t="s">
+        <v>67</v>
+      </c>
+      <c r="O50" t="s">
+        <v>68</v>
+      </c>
+      <c r="P50" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q50"/>
+      <c r="R50"/>
+      <c r="S50"/>
+      <c r="T50" t="s">
+        <v>154</v>
+      </c>
+      <c r="U50" t="s">
+        <v>70</v>
+      </c>
+      <c r="V50" t="s">
+        <v>61</v>
+      </c>
+      <c r="W50" t="s">
+        <v>71</v>
+      </c>
+      <c r="X50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA50"/>
+      <c r="AB50" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1377990</v>
+      </c>
+      <c r="E51" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" t="s">
+        <v>61</v>
+      </c>
+      <c r="I51" t="s">
+        <v>61</v>
+      </c>
+      <c r="J51" t="s">
+        <v>63</v>
+      </c>
+      <c r="K51" t="s">
+        <v>152</v>
+      </c>
+      <c r="L51" t="s">
+        <v>65</v>
+      </c>
+      <c r="M51" t="s">
+        <v>66</v>
+      </c>
+      <c r="N51" t="s">
+        <v>67</v>
+      </c>
+      <c r="O51" t="s">
+        <v>68</v>
+      </c>
+      <c r="P51" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51" t="s">
+        <v>154</v>
+      </c>
+      <c r="U51" t="s">
+        <v>70</v>
+      </c>
+      <c r="V51" t="s">
+        <v>61</v>
+      </c>
+      <c r="W51" t="s">
+        <v>71</v>
+      </c>
+      <c r="X51" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA51"/>
+      <c r="AB51" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1169246</v>
+      </c>
+      <c r="E52" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" t="s">
+        <v>61</v>
+      </c>
+      <c r="J52" t="s">
+        <v>63</v>
+      </c>
+      <c r="K52" t="s">
+        <v>152</v>
+      </c>
+      <c r="L52" t="s">
+        <v>65</v>
+      </c>
+      <c r="M52" t="s">
+        <v>66</v>
+      </c>
+      <c r="N52" t="s">
+        <v>67</v>
+      </c>
+      <c r="O52" t="s">
+        <v>68</v>
+      </c>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52"/>
+      <c r="S52"/>
+      <c r="T52" t="s">
+        <v>154</v>
+      </c>
+      <c r="U52" t="s">
+        <v>90</v>
+      </c>
+      <c r="V52" t="s">
+        <v>88</v>
+      </c>
+      <c r="W52" t="s">
+        <v>91</v>
+      </c>
+      <c r="X52" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC52"/>
+      <c r="AD52"/>
+      <c r="AE52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1145446</v>
+      </c>
+      <c r="E53" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" t="s">
+        <v>181</v>
+      </c>
+      <c r="H53" t="s">
+        <v>61</v>
+      </c>
+      <c r="I53" t="s">
+        <v>61</v>
+      </c>
+      <c r="J53" t="s">
+        <v>63</v>
+      </c>
+      <c r="K53" t="s">
+        <v>152</v>
+      </c>
+      <c r="L53" t="s">
+        <v>65</v>
+      </c>
+      <c r="M53" t="s">
+        <v>66</v>
+      </c>
+      <c r="N53" t="s">
+        <v>67</v>
+      </c>
+      <c r="O53" t="s">
+        <v>68</v>
+      </c>
+      <c r="P53" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q53"/>
+      <c r="R53"/>
+      <c r="S53"/>
+      <c r="T53" t="s">
+        <v>154</v>
+      </c>
+      <c r="U53" t="s">
+        <v>90</v>
+      </c>
+      <c r="V53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W53" t="s">
+        <v>91</v>
+      </c>
+      <c r="X53" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA53"/>
+      <c r="AB53" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>185</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1059190</v>
+      </c>
+      <c r="E54" t="s">
+        <v>186</v>
+      </c>
+      <c r="F54" t="s">
+        <v>88</v>
+      </c>
+      <c r="G54" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" t="s">
+        <v>61</v>
+      </c>
+      <c r="J54" t="s">
+        <v>63</v>
+      </c>
+      <c r="K54" t="s">
+        <v>152</v>
+      </c>
+      <c r="L54" t="s">
+        <v>65</v>
+      </c>
+      <c r="M54" t="s">
+        <v>66</v>
+      </c>
+      <c r="N54" t="s">
+        <v>67</v>
+      </c>
+      <c r="O54" t="s">
+        <v>68</v>
+      </c>
+      <c r="P54" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54"/>
+      <c r="T54" t="s">
+        <v>154</v>
+      </c>
+      <c r="U54" t="s">
+        <v>90</v>
+      </c>
+      <c r="V54" t="s">
+        <v>88</v>
+      </c>
+      <c r="W54" t="s">
+        <v>91</v>
+      </c>
+      <c r="X54" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA54"/>
+      <c r="AB54" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>192</v>
+      </c>
+      <c r="D55" t="n">
+        <v>975334</v>
+      </c>
+      <c r="E55" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" t="s">
+        <v>88</v>
+      </c>
+      <c r="G55" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" t="s">
+        <v>61</v>
+      </c>
+      <c r="J55" t="s">
+        <v>63</v>
+      </c>
+      <c r="K55" t="s">
+        <v>152</v>
+      </c>
+      <c r="L55" t="s">
+        <v>65</v>
+      </c>
+      <c r="M55" t="s">
+        <v>66</v>
+      </c>
+      <c r="N55" t="s">
+        <v>67</v>
+      </c>
+      <c r="O55" t="s">
+        <v>68</v>
+      </c>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55"/>
+      <c r="S55"/>
+      <c r="T55" t="s">
+        <v>154</v>
+      </c>
+      <c r="U55" t="s">
+        <v>90</v>
+      </c>
+      <c r="V55" t="s">
+        <v>88</v>
+      </c>
+      <c r="W55" t="s">
+        <v>91</v>
+      </c>
+      <c r="X55" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA55"/>
+      <c r="AB55" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="s">
+        <v>196</v>
+      </c>
+      <c r="D56" t="n">
+        <v>729081</v>
+      </c>
+      <c r="E56" t="s">
+        <v>87</v>
+      </c>
+      <c r="F56" t="s">
+        <v>88</v>
+      </c>
+      <c r="G56" t="s">
+        <v>177</v>
+      </c>
+      <c r="H56" t="s">
+        <v>61</v>
+      </c>
+      <c r="I56" t="s">
+        <v>61</v>
+      </c>
+      <c r="J56" t="s">
+        <v>63</v>
+      </c>
+      <c r="K56" t="s">
+        <v>152</v>
+      </c>
+      <c r="L56" t="s">
+        <v>65</v>
+      </c>
+      <c r="M56" t="s">
+        <v>66</v>
+      </c>
+      <c r="N56" t="s">
+        <v>67</v>
+      </c>
+      <c r="O56" t="s">
+        <v>68</v>
+      </c>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56"/>
+      <c r="T56" t="s">
+        <v>154</v>
+      </c>
+      <c r="U56" t="s">
+        <v>90</v>
+      </c>
+      <c r="V56" t="s">
+        <v>88</v>
+      </c>
+      <c r="W56" t="s">
+        <v>91</v>
+      </c>
+      <c r="X56" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC56"/>
+      <c r="AD56"/>
+      <c r="AE56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" t="n">
+        <v>662642</v>
+      </c>
+      <c r="E57" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" t="s">
+        <v>61</v>
+      </c>
+      <c r="I57" t="s">
+        <v>61</v>
+      </c>
+      <c r="J57" t="s">
+        <v>63</v>
+      </c>
+      <c r="K57" t="s">
+        <v>152</v>
+      </c>
+      <c r="L57" t="s">
+        <v>65</v>
+      </c>
+      <c r="M57" t="s">
+        <v>66</v>
+      </c>
+      <c r="N57" t="s">
+        <v>67</v>
+      </c>
+      <c r="O57" t="s">
+        <v>68</v>
+      </c>
+      <c r="P57" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57"/>
+      <c r="T57" t="s">
+        <v>154</v>
+      </c>
+      <c r="U57" t="s">
+        <v>70</v>
+      </c>
+      <c r="V57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W57" t="s">
+        <v>71</v>
+      </c>
+      <c r="X57" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA57"/>
+      <c r="AB57" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="s">
+        <v>202</v>
+      </c>
+      <c r="D58" t="n">
+        <v>532045</v>
+      </c>
+      <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G58" t="s">
+        <v>203</v>
+      </c>
+      <c r="H58" t="s">
+        <v>61</v>
+      </c>
+      <c r="I58" t="s">
+        <v>61</v>
+      </c>
+      <c r="J58" t="s">
+        <v>63</v>
+      </c>
+      <c r="K58" t="s">
+        <v>152</v>
+      </c>
+      <c r="L58" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" t="s">
+        <v>66</v>
+      </c>
+      <c r="N58" t="s">
+        <v>67</v>
+      </c>
+      <c r="O58" t="s">
+        <v>68</v>
+      </c>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="S58"/>
+      <c r="T58" t="s">
+        <v>154</v>
+      </c>
+      <c r="U58" t="s">
+        <v>90</v>
+      </c>
+      <c r="V58"/>
+      <c r="W58" t="s">
+        <v>91</v>
+      </c>
+      <c r="X58" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC58"/>
+      <c r="AD58"/>
+      <c r="AE58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>205</v>
+      </c>
+      <c r="D59" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E59" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" t="s">
+        <v>206</v>
+      </c>
+      <c r="H59" t="s">
+        <v>61</v>
+      </c>
+      <c r="I59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J59" t="s">
+        <v>63</v>
+      </c>
+      <c r="K59" t="s">
+        <v>152</v>
+      </c>
+      <c r="L59" t="s">
+        <v>65</v>
+      </c>
+      <c r="M59" t="s">
+        <v>66</v>
+      </c>
+      <c r="N59" t="s">
+        <v>67</v>
+      </c>
+      <c r="O59" t="s">
+        <v>68</v>
+      </c>
+      <c r="P59" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q59"/>
+      <c r="R59"/>
+      <c r="S59"/>
+      <c r="T59" t="s">
+        <v>154</v>
+      </c>
+      <c r="U59" t="s">
+        <v>70</v>
+      </c>
+      <c r="V59" t="s">
+        <v>61</v>
+      </c>
+      <c r="W59" t="s">
+        <v>71</v>
+      </c>
+      <c r="X59" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA59"/>
+      <c r="AB59" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" t="n">
+        <v>219333</v>
+      </c>
+      <c r="E60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60" t="s">
+        <v>88</v>
+      </c>
+      <c r="G60" t="s">
+        <v>177</v>
+      </c>
+      <c r="H60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I60" t="s">
+        <v>61</v>
+      </c>
+      <c r="J60" t="s">
+        <v>63</v>
+      </c>
+      <c r="K60" t="s">
+        <v>152</v>
+      </c>
+      <c r="L60" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" t="s">
+        <v>66</v>
+      </c>
+      <c r="N60" t="s">
+        <v>67</v>
+      </c>
+      <c r="O60" t="s">
+        <v>68</v>
+      </c>
+      <c r="P60"/>
+      <c r="Q60"/>
+      <c r="R60"/>
+      <c r="S60"/>
+      <c r="T60" t="s">
+        <v>154</v>
+      </c>
+      <c r="U60" t="s">
+        <v>90</v>
+      </c>
+      <c r="V60" t="s">
+        <v>88</v>
+      </c>
+      <c r="W60" t="s">
+        <v>91</v>
+      </c>
+      <c r="X60" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC60"/>
+      <c r="AD60"/>
+      <c r="AE60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="s">
+        <v>211</v>
+      </c>
+      <c r="D61" t="n">
+        <v>141098</v>
+      </c>
+      <c r="E61" t="s">
+        <v>60</v>
+      </c>
+      <c r="F61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" t="s">
+        <v>212</v>
+      </c>
+      <c r="H61" t="s">
+        <v>61</v>
+      </c>
+      <c r="I61" t="s">
+        <v>61</v>
+      </c>
+      <c r="J61" t="s">
+        <v>63</v>
+      </c>
+      <c r="K61" t="s">
+        <v>152</v>
+      </c>
+      <c r="L61" t="s">
+        <v>65</v>
+      </c>
+      <c r="M61" t="s">
+        <v>66</v>
+      </c>
+      <c r="N61" t="s">
+        <v>67</v>
+      </c>
+      <c r="O61" t="s">
+        <v>68</v>
+      </c>
+      <c r="P61" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="S61"/>
+      <c r="T61" t="s">
+        <v>154</v>
+      </c>
+      <c r="U61" t="s">
+        <v>70</v>
+      </c>
+      <c r="V61" t="s">
+        <v>61</v>
+      </c>
+      <c r="W61" t="s">
+        <v>71</v>
+      </c>
+      <c r="X61" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA61"/>
+      <c r="AB61" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4604,15 +6148,15 @@
         <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B2" t="n">
         <v>7</v>
@@ -4623,23 +6167,34 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>29097937</v>
+        <v>16006648</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>29097937</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="n">
         <v>22</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>49915410</v>
       </c>
     </row>
